--- a/Result/checksun_type/輪胎.xlsx
+++ b/Result/checksun_type/輪胎.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>49.95</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>50.13</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>47.19</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>50.13</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>47.19</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>2760254.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>2489543.8</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>2489543.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>2608342.2</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>2056931.92</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>2056931.92</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>116547.446286709</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>2760254</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>2760254.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>49.95</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>50.11</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>47.05</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>50.11</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>47.05</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>2576995.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>2361328.0</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>2361328</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>2573029.5</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>2029667.66</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>2029667.66</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>110121.6442078613</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>2576995</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>2576995.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>50.03</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>50.11</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>46.92</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>50.11</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>46.92</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>3563323.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>2348089.0</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>2348089</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>2549300.0</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>1995061.6</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>1995061.6</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>116643.9039449403</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>3563323</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>3563323.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>50.0</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>50.08</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>46.78</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>50.08</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>46.78</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>1902947.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>2333703.0</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>2333703</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>2385178.1</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>1930653.14</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>1930653.14</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>16117.56414273381</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>1902947</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>1902947.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>49.8</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>50.01</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>46.64</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>50.01</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>46.64</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>1644200.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>2577326.8</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>2577326.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>2288006.9</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>1901183.2</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>1901183.2</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>49830.30856305594</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>1644200</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>1644200.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>49.74</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>49.96</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>46.51</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>49.96</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>46.51</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>2119175.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>2727140.6</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>2727140.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>2257097.1</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>1875176.74</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>1875176.74</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>123934.6110005495</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>2119175</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>2119175.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>49.74</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>49.92</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>46.37</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>49.92</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>46.37</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>2510800.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>2784731.0</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>2784731</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>2228150.6</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>1847608.44</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>1847608.44</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>174481.4855183777</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>2510800</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>2510800.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>49.57</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>49.86</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>46.23</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>49.86</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>46.23</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>3491393.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>2750511.0</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>2750511</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>2348177.7</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>1840232.42</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>1840232.42</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>198500.0032039052</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>3491393</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>3491393.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>49.57</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>49.8</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>46.11</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>46.11</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>3121066.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>2436653.2</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>2436653.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>2112008.7</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>1822330.06</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>1822330.06</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>120659.3497830899</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>3121066</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>3121066.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>49.93000000000001</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>49.75</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>46.0</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>49.75</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>46</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>2393269.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>1998687.0</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>1998687</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>2008014.5</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>1802662.46</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>1802662.46</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>44827.0466896724</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>2393269</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>2393269.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>50.29</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>49.67</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>45.89</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>49.67</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>45.89</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>2407127.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>1787053.6</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>1787053.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>1879214.6</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>1779185.08</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>1779185.08</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>12872.46917444491</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>2407127</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>2407127.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>35.61</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>36.04</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>33.85</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>36.04</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>33.85</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>10003939.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>16812721.4</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>16812721.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>28955598.5</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>37495260.14</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>37495260.14</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-4963789.006092828</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>10003939</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>10003939.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>35.49</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>36.15</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>33.64</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>36.15</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>33.64</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>16335914.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>24791136.2</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>24791136.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>29744586.4</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>37462800.8</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>37462800.8</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-4227662.37471519</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>16335914</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>16335914.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>35.94</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>36.29</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>33.43</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>36.29</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>33.43</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>11426356.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>28405642.0</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>28405642</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>30635525.9</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>37276453.84</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>37276453.84</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-3703490.852221593</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>11426356</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>11426356.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>36.5</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>36.41</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>33.23</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>36.41</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>33.23</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>23070340.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>40583749.8</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>40583749.8</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>31288459.2</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>37153017.02</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>37153017.02</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-2296382.789651394</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>23070340</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>23070340.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>36.73</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>36.54</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>33.05</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>36.54</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>33.05</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>23227058.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>39483592.2</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>39483592.2</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>32054656.6</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>36851291.98</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>36851291.98</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-1451784.457777843</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>23227058</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>23227058.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>36.55</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>36.61</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>32.83</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>36.61</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>32.83</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>49896013.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>41098475.6</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>41098475.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>35111442.6</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>36487231.22</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>36487231.22</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-210157.1816092804</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>49896013</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>49896013.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>36.48</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>36.7</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>32.65</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>32.65</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>34408443.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>34698036.6</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>34698036.6</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>33253068.6</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>35584667.3</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>35584667.3</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-1286286.352025293</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>34408443</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>34408443.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>35.92</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>36.71</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>32.41</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>36.71</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>32.41</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>72316895.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>32865409.8</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>32865409.8</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>37547059.9</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>35339260.36</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>35339260.36</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-1118292.440047257</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>72316895</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>72316895.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>35.37</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>36.63</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>32.15</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>36.63</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>32.15</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>17569552.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>21993168.6</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>21993168.6</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>35485008.4</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>34069635.44</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>34069635.44</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-4899981.978648372</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>17569552</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>17569552.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>35.11</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>36.68</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>31.93</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>36.68</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>31.93</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>31301475.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>24625721.0</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>24625721</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>38550535.3</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>33946568.62</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>33946568.62</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-4261609.498841092</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>31301475</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>31301475.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>35.06</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>36.67</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>31.73</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>36.67</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>31.73</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>17893818.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>29124409.6</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>29124409.6</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>39927956.0</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>33607601.62</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>33607601.62</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-4668725.938443527</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>17893818</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>17893818.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>20.39</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>20.42</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>20.33</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>20.42</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>20.33</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>3111603.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>7746104.8</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>7746104.8</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>9050560.6</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>10123667.06</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>10123667.06</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-771459.655962158</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>3111603</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>3111603.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>20.32</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>20.42</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>20.32</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>20.42</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>20.32</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>7571166.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>8563180.4</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>8563180.4</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>11611277.8</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>10267424.2</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>10267424.2</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-297801.5701538436</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>7571166</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>7571166.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>20.32</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>20.41</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>20.33</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>20.41</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>20.33</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>16673233.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>8717070.2</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>8717070.199999999</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>11266208.8</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>10273960.5</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>10273960.5</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-88321.71292218566</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>16673233</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>16673233.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>20.28</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>20.41</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>20.33</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>20.41</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>20.33</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>7787838.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>7789054.2</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>7789054.2</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>10120826.8</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>10049815.34</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>10049815.34</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-761131.8914154526</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>7787838</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>7787838.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>20.47</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>20.4</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>20.33</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>20.33</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>3586684.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>8268244.0</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>8268244</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>10538446.3</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>10010900.14</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>10010900.14</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-743099.4002838545</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>3586684</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>3586684.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>20.66</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>20.4</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>20.34</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>20.34</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>7196981.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>10355016.4</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>10355016.4</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>11515321.2</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>10079136.34</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>10079136.34</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-240675.7915142905</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>7196981</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>7196981.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>20.85</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>20.39</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>20.35</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>20.39</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>20.35</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>8340615.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>14659375.2</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>14659375.2</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>11858116.5</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>10161117.42</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>10161117.42</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>98850.2492820248</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>8340615</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>8340615.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>20.89</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>20.38</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>20.35</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>20.38</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>20.35</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>12033153.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>13815347.4</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>13815347.4</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>12611250.0</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>10116463.34</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>10116463.34</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>457824.8700881209</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>12033153</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>12033153.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>20.88</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>20.38</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>20.35</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>20.38</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>20.35</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>10183787.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>12452599.4</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>12452599.4</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>12062049.2</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>10008415.46</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>10008415.46</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>558665.79730797</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>10183787</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>10183787.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>20.73</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>20.33</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>20.33</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>20.33</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>20.33</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>14020546.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>12808648.6</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>12808648.6</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>11848845.6</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>10016520.52</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>10016520.52</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>880918.2720038947</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>14020546</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>14020546.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>20.59</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>20.26</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>20.32</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>20.26</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>20.32</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>28718775.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>12675626.0</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>12675626</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>10947329.1</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>10085969.44</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>10085969.44</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>898736.261855077</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>28718775</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>28718775.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>19.83</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>19.69</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>19.56</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>19.69</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>19.56</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>4772715.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>8568182.0</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>8568182</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>12540322.7</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>9716875.84</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>9716875.84</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-514431.7435085755</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>4772715</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>4772715.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>19.68</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>19.69</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>19.56</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>19.69</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>19.56</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>6270038.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>10013239.4</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>10013239.4</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>12492670.5</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>9767333.66</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>9767333.66</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-98755.1101299338</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>6270038</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>6270038.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>19.64</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>19.7</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>19.57</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>19.57</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>9560056.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>11858500.4</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>11858500.4</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>12158130.3</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>9884923.4</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>9884923.4</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>338168.155772768</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>9560056</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>9560056.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>19.69</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>19.68</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>19.58</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>19.68</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>19.58</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>7704246.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>12926009.4</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>12926009.4</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>12343795.4</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>9938983.82</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>9938983.82</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>597764.8872133158</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>7704246</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>7704246.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>19.71</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>19.7</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>19.6</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>19.6</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>14533855.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>15923906.4</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>15923906.4</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>12138484.6</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>9970530.48</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>9970530.48</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>1146105.40044219</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>14533855</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>14533855.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>19.59</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>19.7</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>19.61</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>19.61</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>11998002.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>16512463.4</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>16512463.4</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>11779440.5</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>9887302.3</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>9887302.300000001</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>1156772.833610507</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>11998002</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>11998002.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>19.63</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>19.73</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>19.64</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>19.73</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>19.64</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>15496343.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>14972101.6</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>14972101.6</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>11232403.9</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>9953079.7</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>9953079.699999999</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>1402397.244079156</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>15496343</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>15496343.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>19.56</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>19.74</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>19.65</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>19.74</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>19.65</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>14897601.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>12457760.2</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>12457760.2</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>10341626.7</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>9752672.9</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>9752672.9</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>1328381.393174399</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>14897601</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>14897601.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>19.37</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>19.71</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>19.65</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>19.71</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>19.65</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>22693731.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>11761581.4</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>11761581.4</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>9475789.4</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>9540707.58</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>9540707.58</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>1239353.199268518</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>22693731</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>22693731.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>19.3</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>19.68</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>19.66</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>19.68</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>19.66</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>17476640.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>8353062.8</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>8353062.8</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>7990361.3</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>9181936.96</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>9181936.960000001</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>232607.8080005273</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>17476640</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>17476640.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>19.44</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>19.69</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>19.67</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>19.69</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>19.67</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>4296193.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>7046417.6</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>7046417.6</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>7117278.0</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>9005352.36</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>9005352.359999999</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>-654933.2798109073</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>4296193</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>4296193.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>37.35</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>36.61</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>38.16</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>36.61</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>38.16</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>27239652.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>60162699.8</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>60162699.8</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>56617601.5</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>64016109.3</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>64016109.3</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>-477547.0708449036</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>27239652</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>27239652.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>37.16</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>36.59</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>38.21</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>36.59</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>38.21</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>56982984.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>65977529.4</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>65977529.4</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>56384359.7</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>64897381.3</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>64897381.3</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>2117883.218877524</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>56982984</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>56982984.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>37.02</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>36.63</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>38.28</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>36.63</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>38.28</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>62466405.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>65894200.8</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>65894200.8</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>54463792.2</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>65064891.02</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>65064891.02</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>2563216.517806791</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>62466405</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>62466405.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>36.68</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>36.62</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>38.32</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>36.62</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>38.32</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>53626604.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>60093570.8</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>60093570.8</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>51410984.0</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>67161613.88</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>67161613.88</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>2520354.104926929</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>53626604</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>53626604.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>36.54</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>36.66</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>38.39</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>36.66</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>38.39</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>100497854.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>61207026.0</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>61207026</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>48423882.3</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>68423913.04</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>68423913.04000001</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>3316230.975636877</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>100497854</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>100497854.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>36.17</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>36.67</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>38.46</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>36.67</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>38.46</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>56313800.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>53072503.2</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>53072503.2</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>42015114.9</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>70074786.1</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>70074786.09999999</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>-687158.5296216458</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>56313800</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>56313800.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>36.27</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>36.76</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>38.54</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>36.76</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>38.54</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>56566341.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>46791190.0</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>46791190</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>44089008.6</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>72243776.2</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>72243776.2</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>-1647739.23250448</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>56566341</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>56566341.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>36.36</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>36.88</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>38.62</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>36.88</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>38.62</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>33463255.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>43033383.6</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>43033383.6</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>41597501.0</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>78188187.3</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>78188187.3</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>-2988207.51403337</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>33463255</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>33463255.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>36.48999999999999</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>36.94</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>38.68</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>36.94</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>38.68</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>59193880.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>42728397.2</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>42728397.2</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>41443168.3</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>78718752.88</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>78718752.88</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>-2321109.86214488</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>59193880</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>59193880.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>36.56</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>36.98</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>38.72</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>36.98</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>38.72</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>59825240.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>35640738.6</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>35640738.6</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>40442022.2</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>79336942.24</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>79336942.23999999</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>-4042069.114370428</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>59825240</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>59825240.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>36.72</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>37.06</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>38.79</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>37.06</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>38.79</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>24907234.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>30957726.6</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>30957726.6</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>40787702.8</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>81612720.16</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>81612720.16</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>-6423868.434893698</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>24907234</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>24907234.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
